--- a/nfl-backend/data_delivery/nfl_feature_workbook_2026-09-24.xlsx
+++ b/nfl-backend/data_delivery/nfl_feature_workbook_2026-09-24.xlsx
@@ -8,9 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFE Run Detail" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Fold Detail" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Pool" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Features (Master)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Production (23)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Candidates" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFE Run Detail" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Fold Detail" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Redundancy" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Gaps" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glossary" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Pool" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,7 +69,7 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -433,106 +441,1921 @@
   </sheetPr>
   <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NFL Feature Selection Decision Workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Trace</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>nfl_feature_selection_20260924.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Run mode</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>full_history</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Production width before run</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pool size</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Trials scored</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Committed trials</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Selected columns (record-only)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>elo_diff, win_pct_diff, rest_days_diff, is_dome_home, ewm_net_pts_diff, ewm_ypp_diff, pace_plays_min_diff, rest_short_diff, div_game, travel_miles_diff, altitude_home, prime_time, elo_home, elo_away, win_pct_home, win_pct_away, ewm_net_pts_home, ewm_net_pts_away, ewm_ypp_home, ewm_ypp_away, rest_days_home, rest_days_away, is_home</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Default governance: this workbook does not change production. Adoption is explicit.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C00000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NFL Feature Selection Decision Workbook</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="n"/>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Non-null games</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Coverage %</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Scored rows</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Trace</t>
+          <t>ewm_ypp_diff</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>nfl_feature_selection_20260924.json</t>
-        </is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2111</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Run mode</t>
+          <t>pace_plays_min_diff</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>full_history</t>
-        </is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2111</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Production width before run</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>23</v>
+          <t>is_dome_home</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2118</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Pool size</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>23</v>
+          <t>ewm_ypp_away</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2126</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Trials scored</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>23</v>
+          <t>ewm_ypp_home</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2128</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Committed trials</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>0</v>
+          <t>win_pct_diff</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Selected columns (record-only)</t>
+          <t>rest_days_diff</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>elo_diff, win_pct_diff, rest_days_diff, is_dome_home, ewm_net_pts_diff, ewm_ypp_diff, pace_plays_min_diff, rest_short_diff, div_game, travel_miles_diff, altitude_home, prime_time, elo_home, elo_away, win_pct_home, win_pct_away, ewm_net_pts_home, ewm_net_pts_away, ewm_ypp_home, ewm_ypp_away, rest_days_home, rest_days_away, is_home</t>
-        </is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2159</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_diff</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2159</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Default governance: this workbook does not change production. Adoption is explicit.</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
+          <t>rest_short_diff</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_away</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_away</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_away</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_home</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_home</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_home</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>travel_miles_diff</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2154</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>altitude_home</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2154</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>div_game</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>prime_time</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>elo_home</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>elo_away</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Plain-English Description</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Point-in-time rule</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Missing-value policy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>altitude_home</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Game-venue elevation in feet</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>altitude_ft of the game stadium</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>venue attribute known before kickoff</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the venue is missing from the table</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>committed nfl_stadiums.csv (SRTM/Open-Elevation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>div_game</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Division matchup flag</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>1.0 when home and away share a division else 0.0</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>known before kickoff</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the source field is missing</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedule div_game field</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>elo_away</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Away team's pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>team Elo entering kickoff (away side of elo_diff)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>rating entering kickoff; updated only AFTER a game settles</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>ELO_PRIOR (1500) for a team's first-ever game; never NaN</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules (all decided REG games, 2018 warmup onward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>elo_home_entering - elo_away_entering; Elo update r += K*(actual - expected), expected = 1/(1+10**((r_opp - r_self)/400)); actual = 1 win / 0 loss / 0.5 tie</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>rating entering kickoff; updated only AFTER a game settles</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>ELO_PRIOR (1500) for a team's first-ever game; never NaN</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules (all decided REG games, 2018 warmup onward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>elo_home</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Home team's pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>team Elo entering kickoff (home side of elo_diff)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>rating entering kickoff; updated only AFTER a game settles</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>ELO_PRIOR (1500) for a team's first-ever game; never NaN</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules (all decided REG games, 2018 warmup onward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_away</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Away team's exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ewm(halflife=2).mean() of the team's net points (for - against) over strictly-prior games</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>per-team ewm over prior games then shift(1)</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the team has no prior games</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>decided game scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_diff</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ewm(halflife=2).mean() of the team's net points (for - against) over strictly-prior games</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>per-team ewm over prior games then shift(1)</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the team has no prior games</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>decided game scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_home</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Home team's exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ewm(halflife=2).mean() of the team's net points (for - against) over strictly-prior games</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>per-team ewm over prior games then shift(1)</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the team has no prior games</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>decided game scores</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_away</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Away team's exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ewm(halflife=2).mean() of the team's game-level yards_gained/n_plays over strictly-prior games</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>per-team ewm over prior games then shift(1)</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>NaN when no prior games or PBP unavailable for a season</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>nflverse play-by-play</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_diff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>ewm(halflife=2).mean() of the team's game-level yards_gained/n_plays over strictly-prior games</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>per-team ewm over prior games then shift(1)</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>NaN when no prior games or PBP unavailable for a season</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>nflverse play-by-play</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_home</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Home team's exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ewm(halflife=2).mean() of the team's game-level yards_gained/n_plays over strictly-prior games</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>per-team ewm over prior games then shift(1)</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>NaN when no prior games or PBP unavailable for a season</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>nflverse play-by-play</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>is_dome_home</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Home venue roof is a dome (or closed retractable)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1.0 if roof in {dome, closed}; 0.0 if outdoors; NaN unknown</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>venue attribute known before kickoff</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>NaN when roof is unknown/unlisted (e.g. international sites); never fabricated</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedule roof field</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Constant 1.0 anchor for the home-field edge</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>constant 1.0 on every row</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>structural — no data dependency</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>never missing</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>structural constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>pace_plays_min_diff</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away trailing plays per minute</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>trailing 4-game mean of n_plays/elapsed_min per game</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>per-team rolling(4).mean().shift(1)</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>NaN when prior games lack clock data</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>nflverse play-by-play clock</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>prime_time</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Evening-kickoff flag</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1.0 when ET kickoff hour &gt;= 17 else 0.0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>schedule fact known before kickoff</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>NaN when gametime is missing</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedule gametime (ET)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_away</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Away team's days since its previous game</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>(gameday_t - gameday_{t-1}).days for the away team</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>days since the team's own strictly-prior game</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>NaN for a team's first game of the window; in-model handling</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_diff</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away days since each team's previous game</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>(gameday_t - gameday_{t-1}).days per team</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>days since the team's own strictly-prior game</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>NaN for a team's first game of the window; in-model handling</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_home</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Home team's days since its previous game</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>(gameday_t - gameday_{t-1}).days for the home team</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>days since the team's own strictly-prior game</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>NaN for a team's first game of the window; in-model handling</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>rest_short_diff</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away short-rest flag (rest &lt; 7 days)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1.0 when rest_days &lt; 7 else 0.0; home flag minus away flag</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>function of the team's strictly-prior game date</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>NaN when either team has no prior game</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>nflverse schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>travel_miles_diff</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away distance traveled to the venue (miles)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>haversine(team home stadium, game stadium) home minus away; earth radius 3958.8 mi</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>venue geography, known before kickoff</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>NaN when a stadium is missing from the table; never fabricated</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>committed nfl_stadiums.csv (real coordinates) + nflverse stadium names</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_away</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Away team's trailing win percentage</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>mean(team_win) over the away team's prior 12 games (ties = 0.5)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>per-team rolling(12).mean().shift(1) — current and future games excluded</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the team has no prior games; in-model handling</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>decided game outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_diff</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away trailing win percentage</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>mean(team_win) over the team's prior 12 games (ties = 0.5)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>per-team rolling(12).mean().shift(1) — current and future games excluded</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the team has no prior games; in-model handling</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>decided game outcomes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_home</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Home team's trailing win percentage</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>mean(team_win) over the home team's prior 12 games (ties = 0.5)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>per-team rolling(12).mean().shift(1) — current and future games excluded</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>NaN when the team has no prior games; in-model handling</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>decided game outcomes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tested_in_trace</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_diff</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_diff</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>is_dome_home</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_diff</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_diff</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>pace_plays_min_diff</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>rest_short_diff</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>div_game</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>travel_miles_diff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>altitude_home</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>prime_time</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>elo_home</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>elo_away</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_home</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_away</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_home</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_away</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_home</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_away</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_home</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_away</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>production contract</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="b">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -542,6 +2365,2403 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NFL Feature Selection Decision Workbook</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Trace</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>nfl_feature_selection_20260924.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Trace schema</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>nfl-rfe-v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Run date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Run mode</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>full_history</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Scoring population (games)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>2159</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Production width before run</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Candidate pool size</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Full validation pool</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Trials scored</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Committed trials</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Failed trials</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Selected columns (record-only)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff, win_pct_diff, rest_days_diff, is_dome_home, ewm_net_pts_diff, ewm_ypp_diff, pace_plays_min_diff, rest_short_diff, div_game, travel_miles_diff, altitude_home, prime_time, elo_home, elo_away, win_pct_home, win_pct_away, ewm_net_pts_home, ewm_net_pts_away, ewm_ypp_home, ewm_ypp_away, rest_days_home, rest_days_away, is_home</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Default governance: this workbook does not change production. Adoption is explicit.</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Commit rule: a trial commits only when its paired log-loss gain clears max(0.0005, 2 x paired SE) with AUC and ECE guardrails.</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Baseline log-loss</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0.6477273264731944</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Best log-loss reached</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0.6477273264731944</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RFE Run Dashboard</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Trials scored</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Committed removals</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Committed additions</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Failed trials (recorded, non-fatal)</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Features selected (record-only)</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Baseline log-loss</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.6477273264731944</v>
+      </c>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Best log-loss</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.6477273264731944</v>
+      </c>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Baseline AUC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.6761755800772</v>
+      </c>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Best AUC</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.6761755800772</v>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Redundant pairs (|r| &gt;= 0.9)</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Committed changes this run</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Step</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Log-loss gain</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Committed</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00548235"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>In Production</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Plain-English Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>full history (iterative)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_diff</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away trailing win percentage</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>12 games</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_diff</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away days since each team's previous game</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>is_dome_home</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Home venue roof is a dome (or closed retractable)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_diff</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_diff</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>pace_plays_min_diff</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away trailing plays per minute</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4 games</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>rest_short_diff</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away short-rest flag (rest &lt; 7 days)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>div_game</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Schedule / venue</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Division matchup flag</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>travel_miles_diff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away distance traveled to the venue (miles)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>altitude_home</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Game-venue elevation in feet</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>prime_time</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Schedule / venue</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Evening-kickoff flag</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>elo_home</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Home team's pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>full history (iterative)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>elo_away</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Away team's pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>full history (iterative)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_home</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Home team's trailing win percentage</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12 games</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_away</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Away team's trailing win percentage</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12 games</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_home</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Home team's exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_away</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Away team's exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_home</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Home team's exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_away</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Away team's exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_home</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Home team's days since its previous game</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_away</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Away team's days since its previous game</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Constant 1.0 anchor for the home-field edge</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00375623"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>In Production</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Plain-English Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>full history (iterative)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_diff</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away trailing win percentage</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>12 games</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_diff</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away days since each team's previous game</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>is_dome_home</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Home venue roof is a dome (or closed retractable)</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_diff</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_diff</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>pace_plays_min_diff</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away trailing plays per minute</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4 games</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>rest_short_diff</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away short-rest flag (rest &lt; 7 days)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>div_game</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Schedule / venue</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Division matchup flag</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>travel_miles_diff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Team form</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Home minus away distance traveled to the venue (miles)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>altitude_home</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Game-venue elevation in feet</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>prime_time</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Schedule / venue</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Evening-kickoff flag</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>elo_home</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Home team's pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>full history (iterative)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>elo_away</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Away team's pre-game Elo rating</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>full history (iterative)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_home</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Home team's trailing win percentage</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12 games</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_away</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Away team's trailing win percentage</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12 games</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_home</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Home team's exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_away</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Away team's exponentially-weighted net points per game</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_home</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Home team's exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_away</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Away team's exponentially-weighted net yards per play</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>decaying (halflife=2 games)</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_home</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Home team's days since its previous game</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_away</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Away team's days since its previous game</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1 games</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>is_home</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Matchup context</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Constant 1.0 anchor for the home-field edge</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>static pre-game</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C55A11"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="80" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>In Production</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Plain-English Description</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Role in run</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1549,9 +5769,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="009E5EB5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -46867,380 +51088,62 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002F8F83"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>feature</t>
+          <t>Feature A</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>Feature B</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>tested_in_trace</t>
+          <t>Pearson r</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>elo_diff</t>
+          <t>rest_days_home</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>win_pct_diff</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>rest_days_diff</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>is_dome_home</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>ewm_net_pts_diff</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>ewm_ypp_diff</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>pace_plays_min_diff</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>rest_short_diff</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>div_game</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>travel_miles_diff</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>altitude_home</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>prime_time</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>elo_home</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>elo_away</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>win_pct_home</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>win_pct_away</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>ewm_net_pts_home</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>ewm_net_pts_away</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>ewm_ypp_home</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>ewm_ypp_away</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>rest_days_home</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
           <t>rest_days_away</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>is_home</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>production contract</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="b">
-        <v>1</v>
+      <c r="C2" s="2" t="n">
+        <v>0.9991</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>near-duplicate signal — consider one representative</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/nfl-backend/data_delivery/nfl_feature_workbook_2026-09-24.xlsx
+++ b/nfl-backend/data_delivery/nfl_feature_workbook_2026-09-24.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +39,18 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -66,12 +78,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -544,646 +568,1738 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Feature</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Side</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Non-null games</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Coverage %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Scored rows</t>
-        </is>
-      </c>
+          <t>Coverage Gaps — what the API pulls serve vs what production uses</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ewm_ypp_diff</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>2111</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>97.78</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Sections A–E are the MLB-parity gap catalog (authored, grounded in ingestion.py / qb_enrichment.py). The last block is the run's own per-feature non-null coverage. Record-only: nothing here changes production without an explicit adoption run.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>pace_plays_min_diff</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>2111</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>97.78</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>is_dome_home</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Raw level (per side)</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2118</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>SECTION A — API payload inventory: serves vs extracts</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>ewm_ypp_away</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Raw level (per side)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>2126</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>98.47</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>API endpoint</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>What the payload serves</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>What the pipeline extracts today</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>What is left unused</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ewm_ypp_home</t>
+          <t>nflverse play-by-play
+nflreadpy.load_pbp (nflfastR pbp, ~400 cols/play)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>Per play: teams, yards, EPA (play + QB), WPA, air yards, YAC, completion-probability (cpoe), down &amp; distance, formation (shotgun/no-huddle), timeouts, score state, penalties, third/fourth-down conversions, field-goal results, drive metadata — plus the payload's own temp/wind/humidity and roof/surface columns.</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>2128</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>98.56</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>2159</v>
-      </c>
+          <t>Narrowed at load to PBP_NEEDS (21 columns). The game rollup (features.pbp_team_agg) then aggregates ONLY yards_gained and game_seconds_remaining (total yards, plays, pace).</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Everything else — including columns KEPT but never aggregated: epa, qb_epa, interception, fumble_lost, sack, pass_attempt, passing_yards, penalty, penalty_yards, penalty_team, third_down_converted/failed, yardline_100, touchdown, field_goal_result, drive. Also dropped at load: air_yards, yac, cpoe, wpa, down/ydstogo, shotgun/no_huddle, score_differential, timeouts.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>win_pct_diff</t>
+          <t>nflverse schedules
+nflreadpy.load_schedules</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>Per game: betting lines (spread_line, total_line, over_under_line), weather (temp, wind), stadium/roof/surface/location, referee, game_type, overtime, division flag, QB ids/names.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2159</v>
-      </c>
+          <t>20-column keep-list; features use teams/scores/date/week/div_game and QB ids/names (card enrichment).</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Kept-but-unused: roof, stadium, surface, location, referee, game_type. Dropped entirely: spread_line, total_line, over_under_line, temp, wind, weather, overtime — NFL has NO weather and NO market-implied features (MLB has both).</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>rest_days_diff</t>
+          <t>nflverse player stats
+nflreadpy.load_player_stats (all positions)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>Weekly player stats for every position: passing, rushing, receiving volumes and efficiency, ids/names.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2159</v>
-      </c>
+          <t>QB rows only (position == 'QB'): passer-rating components for card enrichment. No model features.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>RB/WR/TE usage (carries, targets, team pass-rate, RB load, WR1 threat), defensive player stats.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ewm_net_pts_diff</t>
+          <t>nflverse teams
+nflreadpy.load_teams</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>Team abbr, full names, conference/division, colors, logos.</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>2159</v>
-      </c>
+          <t>Abbr -&gt; name map for the frontend only.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Conference/division membership (division-rank context), nothing else modeled.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>rest_short_diff</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Diff</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="2" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>win_pct_away</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Raw level (per side)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>SECTION B — Unused payload fields -&gt; candidate features</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="2" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>ewm_net_pts_away</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Raw level (per side)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>2159</v>
-      </c>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Field(s)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>What it is</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Candidate feature</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Impact</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Effort</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>rest_days_away</t>
+          <t>pbp (KEPT)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>epa / qb_epa</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>2142</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>2159</v>
+          <t>Play- and QB-level expected points added.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Trailing EPA/play and EPA-per-dropback diffs (efficiency beyond yards).</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Already in the pull cache — only the rollup is missing.</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>win_pct_home</t>
+          <t>pbp (KEPT)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>interception / fumble_lost</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>2143</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>99.26000000000001</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>2159</v>
+          <t>Turnover events per play.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Trailing turnover-margin EWM; protection/takeaway edge.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Kept in PBP_NEEDS, never aggregated.</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ewm_net_pts_home</t>
+          <t>pbp (KEPT)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>sack / pass_attempt</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>2143</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>99.26000000000001</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>2159</v>
+          <t>Pressure allowed and dropback volume.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sack-rate and dropback-rate diffs (OL + playcalling).</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Kept in PBP_NEEDS, never aggregated.</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>rest_days_home</t>
+          <t>pbp (KEPT)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>third_down_converted / third_down_failed</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>2143</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>99.26000000000001</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>2159</v>
+          <t>Third-down outcomes.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Trailing conversion-rate diff (situational strength).</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Kept in PBP_NEEDS, never aggregated.</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>travel_miles_diff</t>
+          <t>pbp (KEPT)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>penalty / penalty_yards</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2154</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>2159</v>
+          <t>Penalty events and yardage.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Trailing penalty-yards-per-game diff (discipline).</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Kept in PBP_NEEDS, never aggregated.</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>altitude_home</t>
+          <t>pbp (KEPT)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>yardline_100 / touchdown / field_goal_result</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>2154</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>2159</v>
+          <t>Field position, scoring plays, FG outcomes.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Red-zone finish rate, starting-field-position edge, kicker accuracy.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Kept in PBP_NEEDS, never aggregated.</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>elo_diff</t>
+          <t>pbp (dropped)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Diff</t>
+          <t>air_yards / yac / cpoe</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Home − Away (diff)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>2159</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>2159</v>
+          <t>Passing depth, separation after catch, accuracy over expectation.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Trailing passing-depth and accuracy diffs ( qb play quality).</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>One-line additions to PBP_NEEDS + rollup.</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>div_game</t>
+          <t>pbp (dropped)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Game-level flag/context</t>
+          <t>shotgun / no_huddle / drive</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Game-level</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>2159</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>2159</v>
-      </c>
+          <t>Formation tendency and drive counts.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Style/pace complements to the existing plays-per-minute feature.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>prime_time</t>
+          <t>schedules (dropped)</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Game-level flag/context</t>
+          <t>temp / wind / weather</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Game-level</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>2159</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>2159</v>
+          <t>Observed game-day environment.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Wind-speed and temperature bands for outdoor games (MLB weather parity).</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>Payload carries it; no weather feature exists today.</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>elo_home</t>
+          <t>schedules (dropped)</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>spread_line / total_line / over_under_line</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>2159</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>2159</v>
+          <t>Market-implied win margin and total.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Market-anchor features or blend components (MLB market parity).</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Closing lines arrive with the schedule payload.</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>elo_away</t>
+          <t>schedules (KEPT)</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Raw level (per side)</t>
+          <t>roof / surface</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Away</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>2159</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>2159</v>
+          <t>Roof state and playing surface.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>is_dome_home exists; turf-vs-grass interaction still unused.</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>Kept at load, never read by features.</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>player_stats</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>RB carries / WR targets</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Skill-position usage.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Team pass-rate tendency, RB-load and WR1-threat diffs.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Requires removing the QB-only filter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+      <c r="G25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>SECTION C — nflreadpy endpoints never loaded</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Endpoint</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>What it serves</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Feature opportunity</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>load_injuries</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Weekly injury reports with participation status.</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Starter-out availability flags (QB/edge/left-tackle most valuable).</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="n"/>
+      <c r="G28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>load_snap_counts</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Per-player snap counts by week.</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Workload context: RB committees, defensive snap wear.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr"/>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>load_ngs</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Next-Gen Stats: passing/rushing/receiving efficiency.</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Deeper QB/RB quality measures beyond box-score aggregates.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="n"/>
+      <c r="G30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>load_officials</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Per-game officiating crews.</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Crew penalty-rate context (second-order).</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="n"/>
+      <c r="G31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>load_participation</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Advanced participation and alignment data.</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Coverage/pressure context (higher effort).</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>load_pfr</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>PFR advanced passing/rushing metrics.</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Pressure-rate and coverage-grade context.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="n"/>
+      <c r="G33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>load_qbr</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>ESPN QBR (weekly and season).</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>QB quality signal complementary to passer rating.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr"/>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n"/>
+      <c r="B35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n"/>
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="n"/>
+      <c r="G35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>SECTION D — Declared candidates not trialed by this run</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n"/>
+      <c r="C36" s="5" t="n"/>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>No declared candidates in this run (config.RFE_CANDIDATE_COLS is empty) — the sweep was removals-only over the production contract. Declare candidates via RFE_CANDIDATE_COLS / NFL_RFE_ADDITION_MONEYLINE_LIST to trial new features.</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
+      <c r="E38" s="2" t="n"/>
+      <c r="F38" s="2" t="n"/>
+      <c r="G38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>SECTION E — Cataloged but NOT recommended (honesty section)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>Field(s)</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Why not recommended</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>pbp</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>score_differential / wpa / timeouts</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>In-game state — leaks if applied pre-game; kept out on purpose.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>pbp</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>total_line-derived per-play pace</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Already captured by the plays-per-minute feature; no second signal.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>schedules</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>One official per game; tiny signal, heavy cardinality.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>schedules</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>game_type</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Already filtered to regular-season games before features.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>player_stats</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>fantasy points</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Construction artifact, no independent edge.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n"/>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>PER-FEATURE COVERAGE — non-null share in the scored frame</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="n"/>
+      <c r="C47" s="5" t="n"/>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Side</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Non-null games</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>Coverage %</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>Scored rows</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_diff</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2111</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>pace_plays_min_diff</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2111</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>97.78</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>is_dome_home</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2118</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_away</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2126</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>98.47</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>ewm_ypp_home</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2128</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_diff</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_diff</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_diff</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>rest_short_diff</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_away</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_away</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_away</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>win_pct_home</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>ewm_net_pts_home</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>rest_days_home</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>travel_miles_diff</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2154</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>altitude_home</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2154</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>99.77</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>elo_diff</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Diff</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Home − Away (diff)</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>div_game</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>prime_time</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Game-level flag/context</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Game-level</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>elo_home</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Home</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>elo_away</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Raw level (per side)</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Away</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>2159</v>
+      </c>
+      <c r="G70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
           <t>is_home</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>Raw level (per side)</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Home</t>
         </is>
       </c>
-      <c r="D24" s="2" t="n">
+      <c r="D71" s="2" t="n">
         <v>2159</v>
       </c>
-      <c r="E24" s="2" t="n">
+      <c r="E71" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F71" s="2" t="n">
         <v>2159</v>
       </c>
+      <c r="G71" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
